--- a/流程图和上报字段/集团上报数据字段清单_产品版.xlsx
+++ b/流程图和上报字段/集团上报数据字段清单_产品版.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天泽智联\深圳中外运物流有限公司科技兴安暨智慧园区四期项目\静态页面\流程图和上报字段\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天泽智联\深圳中外运物流有限公司科技兴安暨智慧园区四期项目\github生产静态页面\waiyunpinghu\流程图和上报字段\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="15300" activeTab="1"/>
+    <workbookView windowWidth="29868" windowHeight="15300"/>
   </bookViews>
   <sheets>
-    <sheet name="上报字段清单" sheetId="1" r:id="rId1"/>
+    <sheet name="核警后上报数据" sheetId="3" r:id="rId1"/>
     <sheet name="设备清单" sheetId="2" r:id="rId2"/>
+    <sheet name="作废--上报字段清单(查处上报版本)" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,10 +34,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="261">
   <si>
     <r>
-      <t xml:space="preserve">报警事件上报数据字段清单
+      <t xml:space="preserve">报警事件上报数据字段清单（对应的是AI核警中心菜单，无消防设备报警信息）
 </t>
     </r>
     <r>
@@ -50,6 +51,9 @@
     </r>
   </si>
   <si>
+    <t>华南回传数据</t>
+  </si>
+  <si>
     <t>序号</t>
   </si>
   <si>
@@ -65,55 +69,85 @@
     <t>什么时候提供</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
     <t>上报单位</t>
   </si>
   <si>
-    <t>报警所属的单位</t>
-  </si>
-  <si>
-    <t>深圳中外运物流有限公司</t>
+    <t>报警所属单位</t>
+  </si>
+  <si>
+    <t>平湖物流中心</t>
   </si>
   <si>
     <t>每条报警均提供</t>
   </si>
   <si>
+    <t>处置人员手机号码</t>
+  </si>
+  <si>
+    <t>完成现场处理的人员</t>
+  </si>
+  <si>
+    <t>处置人员甲</t>
+  </si>
+  <si>
+    <t>AI任务已完成后提供</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>所属园区</t>
-  </si>
-  <si>
-    <t>报警所属园区或项目</t>
-  </si>
-  <si>
-    <t>平湖物流中心</t>
+    <t>报警编号</t>
+  </si>
+  <si>
+    <t>区分并关联同一条报警及后续结果</t>
+  </si>
+  <si>
+    <t>示例报警0001</t>
+  </si>
+  <si>
+    <t>违规人员手机号码</t>
+  </si>
+  <si>
+    <t>本次确认违规涉及的人员</t>
+  </si>
+  <si>
+    <t>违规人员甲</t>
+  </si>
+  <si>
+    <t>AI任务已完成且登记人员后提供</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>报警来源</t>
+  </si>
+  <si>
+    <t>区分AI识别报警和消防设备报警</t>
+  </si>
+  <si>
+    <t>AI识别报警</t>
+  </si>
+  <si>
+    <t>无需上报</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>报警编号</t>
-  </si>
-  <si>
-    <t>区分并关联同一条报警及后续结果</t>
-  </si>
-  <si>
-    <t>示例报警0001</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>报警来源</t>
-  </si>
-  <si>
-    <t>区分AI识别报警和消防设备报警</t>
-  </si>
-  <si>
-    <t>AI识别报警</t>
+    <t>处理经过</t>
+  </si>
+  <si>
+    <t>现场采取了哪些处理行动</t>
+  </si>
+  <si>
+    <t>现场制止违规并开展安全教育</t>
   </si>
   <si>
     <t>5</t>
@@ -122,12 +156,21 @@
     <t>报警类型</t>
   </si>
   <si>
-    <t>本次发生的违规或异常类型</t>
+    <t>本次发生的违规事件类型</t>
   </si>
   <si>
     <t>货架区未佩戴安全帽</t>
   </si>
   <si>
+    <t>整改措施</t>
+  </si>
+  <si>
+    <t>为消除本次问题采取的措施</t>
+  </si>
+  <si>
+    <t>已按要求佩戴安全帽后恢复作业</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
@@ -140,6 +183,18 @@
     <t>2026-10-22 10:00:00</t>
   </si>
   <si>
+    <t>处置完成时间</t>
+  </si>
+  <si>
+    <t>本次事件处理完成的时间</t>
+  </si>
+  <si>
+    <t>2026-10-22 10:20:00</t>
+  </si>
+  <si>
+    <t>AI完成后提供；消防有外部完成时间时提供</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
@@ -155,6 +210,18 @@
     <t>仅AI报警提供；消防不适用</t>
   </si>
   <si>
+    <t>整改照片</t>
+  </si>
+  <si>
+    <t>证明现场已整改的照片</t>
+  </si>
+  <si>
+    <t>现场整改照片</t>
+  </si>
+  <si>
+    <t>有真实整改照片时提供</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
@@ -167,6 +234,18 @@
     <t>1号仓库 / 1层 / 货架区</t>
   </si>
   <si>
+    <t>处置是否超期</t>
+  </si>
+  <si>
+    <t>是否超过平台配置的处置时限</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>仅已接收AI任务提供；从接收时开始计算</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
@@ -179,13 +258,25 @@
     <t>示例设备0001</t>
   </si>
   <si>
+    <t>处置周期</t>
+  </si>
+  <si>
+    <t>从报警发生到最终完成的总时长</t>
+  </si>
+  <si>
+    <t>20分钟</t>
+  </si>
+  <si>
+    <t>AI任务完成后提供</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
     <t>设备名称</t>
   </si>
   <si>
-    <t>产生报警的摄像机或消防设备名称</t>
+    <t>产生报警的摄像机</t>
   </si>
   <si>
     <t>货架通道摄像头01</t>
@@ -212,10 +303,10 @@
     <t>区域责任人</t>
   </si>
   <si>
-    <t>负责该区域的人员</t>
-  </si>
-  <si>
-    <t>责任人员甲</t>
+    <t>负责该区域的人员（班组多人）</t>
+  </si>
+  <si>
+    <t>责任人员甲、乙、丙等（某个班组所有成员）</t>
   </si>
   <si>
     <t>已明确责任人时提供</t>
@@ -272,7 +363,7 @@
     <t>当前处理状态</t>
   </si>
   <si>
-    <t>AI为待复核、待接收、待处置、已处置或无需处置；消防为待处置、已处置</t>
+    <t>AI为待接收、待处置、已处置；</t>
   </si>
   <si>
     <t>待处置</t>
@@ -359,9 +450,6 @@
     <t>是否超过平台配置的复核时限</t>
   </si>
   <si>
-    <t>否</t>
-  </si>
-  <si>
     <t>仅AI报警提供；从报警发生起计算</t>
   </si>
   <si>
@@ -374,9 +462,6 @@
     <t>接收处置任务的人员</t>
   </si>
   <si>
-    <t>处置人员甲</t>
-  </si>
-  <si>
     <t>AI任务已接收后提供</t>
   </si>
   <si>
@@ -392,345 +477,6 @@
     <t>2026-10-22 10:05:00</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>处置人员</t>
-  </si>
-  <si>
-    <t>完成现场处理的人员</t>
-  </si>
-  <si>
-    <t>AI任务已完成后提供</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>违规人员</t>
-  </si>
-  <si>
-    <t>本次确认违规涉及的人员</t>
-  </si>
-  <si>
-    <t>违规人员甲</t>
-  </si>
-  <si>
-    <t>AI任务已完成且登记人员后提供</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>处理经过</t>
-  </si>
-  <si>
-    <t>现场采取了哪些处理行动</t>
-  </si>
-  <si>
-    <t>现场制止违规并开展安全教育</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>整改措施</t>
-  </si>
-  <si>
-    <t>为消除本次问题采取的措施</t>
-  </si>
-  <si>
-    <t>已按要求佩戴安全帽后恢复作业</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>处置完成时间</t>
-  </si>
-  <si>
-    <t>本次事件处理完成的时间</t>
-  </si>
-  <si>
-    <t>2026-10-22 10:20:00</t>
-  </si>
-  <si>
-    <t>AI完成后提供；消防有外部完成时间时提供</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>整改照片</t>
-  </si>
-  <si>
-    <t>证明现场已整改的照片</t>
-  </si>
-  <si>
-    <t>现场整改照片</t>
-  </si>
-  <si>
-    <t>有真实整改照片时提供</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>处置是否超期</t>
-  </si>
-  <si>
-    <t>是否超过平台配置的处置时限</t>
-  </si>
-  <si>
-    <t>仅已接收AI任务提供；从接收时开始计算</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>处置周期</t>
-  </si>
-  <si>
-    <t>从报警发生到最终完成的总时长</t>
-  </si>
-  <si>
-    <t>20分钟</t>
-  </si>
-  <si>
-    <t>AI任务完成后提供</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>联系时间</t>
-  </si>
-  <si>
-    <t>值守人员进行电话联系的时间</t>
-  </si>
-  <si>
-    <t>2026-10-22 10:10:00</t>
-  </si>
-  <si>
-    <t>每次实际联系后提供，可有多条</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>联系人员</t>
-  </si>
-  <si>
-    <t>发起本次电话联系的值守人员</t>
-  </si>
-  <si>
-    <t>值守人员甲</t>
-  </si>
-  <si>
-    <t>每次实际联系后提供</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>联系对象</t>
-  </si>
-  <si>
-    <t>本次电话联系的人员</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>联系内容</t>
-  </si>
-  <si>
-    <t>催促接收、了解处置进展等内容</t>
-  </si>
-  <si>
-    <t>提醒及时完成整改并提交结果</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>联系结果</t>
-  </si>
-  <si>
-    <t>本次电话沟通的实际结果</t>
-  </si>
-  <si>
-    <t>已联系，对方正在现场处置</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>统计期间</t>
-  </si>
-  <si>
-    <t>本次统计对应的起止日期</t>
-  </si>
-  <si>
-    <t>2026-10-01至2026-10-21</t>
-  </si>
-  <si>
-    <t>汇总数据提供</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>统计截至时间</t>
-  </si>
-  <si>
-    <t>各项数量和处理状态统计到的时间</t>
-  </si>
-  <si>
-    <t>2026-10-22 00:05:00</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>报警总数</t>
-  </si>
-  <si>
-    <t>统计期间内发生的报警数量</t>
-  </si>
-  <si>
-    <t>100条</t>
-  </si>
-  <si>
-    <t>按来源分别提供</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>待复核数量</t>
-  </si>
-  <si>
-    <t>尚未完成复核的AI报警数量</t>
-  </si>
-  <si>
-    <t>10条</t>
-  </si>
-  <si>
-    <t>仅AI报警汇总提供</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>确认违规数量</t>
-  </si>
-  <si>
-    <t>经人工复核确认违规的数量</t>
-  </si>
-  <si>
-    <t>60条</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>误报数量</t>
-  </si>
-  <si>
-    <t>经人工复核判定为误报的数量</t>
-  </si>
-  <si>
-    <t>20条</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>计划内事件数量</t>
-  </si>
-  <si>
-    <t>经人工复核判定为计划内事件的数量</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>待接收数量</t>
-  </si>
-  <si>
-    <t>确认违规但尚未接收的任务数</t>
-  </si>
-  <si>
-    <t>5条</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>待处置数量</t>
-  </si>
-  <si>
-    <t>AI已接收未完成数，或消防外部状态为待处置数</t>
-  </si>
-  <si>
-    <t>AI 15条；消防另行统计</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>已处置数量</t>
-  </si>
-  <si>
-    <t>统计范围内已经完成处置的数量</t>
-  </si>
-  <si>
-    <t>AI 40条；消防另行统计</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>超期待处置数量</t>
-  </si>
-  <si>
-    <t>已接收且尚未完成并超过时限的AI任务数</t>
-  </si>
-  <si>
-    <t>3条</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>报警准确率</t>
-  </si>
-  <si>
-    <t>确认违规数量占确认违规与误报合计的比例</t>
-  </si>
-  <si>
-    <t>75%</t>
-  </si>
-  <si>
-    <t>仅AI报警；无可计算数据时留空</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>处置完成率</t>
-  </si>
-  <si>
-    <t>AI已处置占确认违规的比例；消防已处置占消防报警总数的比例</t>
-  </si>
-  <si>
-    <t>AI 66.7%；消防另行计算</t>
-  </si>
-  <si>
-    <t>依据：当前平台原型标注中的报警、复核、处置、电话记录和统计功能；本表仅定义业务输出内容。</t>
-  </si>
-  <si>
     <t>设备数据字段清单</t>
   </si>
   <si>
@@ -750,6 +496,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>硬件设备型号，如：海康</t>
     </r>
     <r>
@@ -774,6 +525,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>归属的业务区域</t>
     </r>
     <r>
@@ -798,6 +554,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>设备精准物理点位描述，如：原料北大门立柱</t>
     </r>
     <r>
@@ -819,6 +580,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
       <t>IP</t>
     </r>
     <r>
@@ -832,6 +598,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>设备局域网</t>
     </r>
     <r>
@@ -856,6 +627,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>视频通道编号，多路摄像头</t>
     </r>
     <r>
@@ -896,6 +672,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>记录当前设备绑定的</t>
     </r>
     <r>
@@ -943,6 +724,316 @@
   <si>
     <t>设备变更标记：0 - 正常、1 - 下线停用、2 - 设备更换；用于台账变更留痕，触发视频流重新接入</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF172033"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">报警事件上报数据字段清单
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF172033"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="134"/>
+      </rPr>
+      <t>每条明细带报警编号；尚未发生的复核和处置结果留空；消防结果取外部系统。</t>
+    </r>
+  </si>
+  <si>
+    <t>报警所属的单位</t>
+  </si>
+  <si>
+    <t>深圳中外运物流有限公司</t>
+  </si>
+  <si>
+    <t>所属园区</t>
+  </si>
+  <si>
+    <t>报警所属园区或项目</t>
+  </si>
+  <si>
+    <t>本次发生的违规或异常类型</t>
+  </si>
+  <si>
+    <t>产生报警的摄像机或消防设备名称</t>
+  </si>
+  <si>
+    <t>负责该区域的人员</t>
+  </si>
+  <si>
+    <t>责任人员甲</t>
+  </si>
+  <si>
+    <t>AI为待复核、待接收、待处置、已处置或无需处置；消防为待处置、已处置</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>处置人员</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>违规人员</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>联系时间</t>
+  </si>
+  <si>
+    <t>值守人员进行电话联系的时间</t>
+  </si>
+  <si>
+    <t>2026-10-22 10:10:00</t>
+  </si>
+  <si>
+    <t>每次实际联系后提供，可有多条</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>联系人员</t>
+  </si>
+  <si>
+    <t>发起本次电话联系的值守人员</t>
+  </si>
+  <si>
+    <t>值守人员甲</t>
+  </si>
+  <si>
+    <t>每次实际联系后提供</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>联系对象</t>
+  </si>
+  <si>
+    <t>本次电话联系的人员</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>联系内容</t>
+  </si>
+  <si>
+    <t>催促接收、了解处置进展等内容</t>
+  </si>
+  <si>
+    <t>提醒及时完成整改并提交结果</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>联系结果</t>
+  </si>
+  <si>
+    <t>本次电话沟通的实际结果</t>
+  </si>
+  <si>
+    <t>已联系，对方正在现场处置</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>统计期间</t>
+  </si>
+  <si>
+    <t>本次统计对应的起止日期</t>
+  </si>
+  <si>
+    <t>2026-10-01至2026-10-21</t>
+  </si>
+  <si>
+    <t>汇总数据提供</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>统计截至时间</t>
+  </si>
+  <si>
+    <t>各项数量和处理状态统计到的时间</t>
+  </si>
+  <si>
+    <t>2026-10-22 00:05:00</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>报警总数</t>
+  </si>
+  <si>
+    <t>统计期间内发生的报警数量</t>
+  </si>
+  <si>
+    <t>100条</t>
+  </si>
+  <si>
+    <t>按来源分别提供</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>待复核数量</t>
+  </si>
+  <si>
+    <t>尚未完成复核的AI报警数量</t>
+  </si>
+  <si>
+    <t>10条</t>
+  </si>
+  <si>
+    <t>仅AI报警汇总提供</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>确认违规数量</t>
+  </si>
+  <si>
+    <t>经人工复核确认违规的数量</t>
+  </si>
+  <si>
+    <t>60条</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>误报数量</t>
+  </si>
+  <si>
+    <t>经人工复核判定为误报的数量</t>
+  </si>
+  <si>
+    <t>20条</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>计划内事件数量</t>
+  </si>
+  <si>
+    <t>经人工复核判定为计划内事件的数量</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>待接收数量</t>
+  </si>
+  <si>
+    <t>确认违规但尚未接收的任务数</t>
+  </si>
+  <si>
+    <t>5条</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>待处置数量</t>
+  </si>
+  <si>
+    <t>AI已接收未完成数，或消防外部状态为待处置数</t>
+  </si>
+  <si>
+    <t>AI 15条；消防另行统计</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>已处置数量</t>
+  </si>
+  <si>
+    <t>统计范围内已经完成处置的数量</t>
+  </si>
+  <si>
+    <t>AI 40条；消防另行统计</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>超期待处置数量</t>
+  </si>
+  <si>
+    <t>已接收且尚未完成并超过时限的AI任务数</t>
+  </si>
+  <si>
+    <t>3条</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>报警准确率</t>
+  </si>
+  <si>
+    <t>确认违规数量占确认违规与误报合计的比例</t>
+  </si>
+  <si>
+    <t>75%</t>
+  </si>
+  <si>
+    <t>仅AI报警；无可计算数据时留空</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>处置完成率</t>
+  </si>
+  <si>
+    <t>AI已处置占确认违规的比例；消防已处置占消防报警总数的比例</t>
+  </si>
+  <si>
+    <t>AI 66.7%；消防另行计算</t>
+  </si>
+  <si>
+    <t>依据：当前平台原型标注中的报警、复核、处置、电话记录和统计功能；本表仅定义业务输出内容。</t>
+  </si>
 </sst>
 </file>
 
@@ -954,7 +1045,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -976,11 +1067,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF24344D"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
@@ -988,6 +1074,46 @@
     <font>
       <sz val="10"/>
       <color rgb="FF8190A5"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
@@ -1149,7 +1275,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1165,6 +1291,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0F5FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1481,199 +1619,230 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="49" applyFill="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2199,7 +2368,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="浅色系标题行表格样式_b4126a" count="10" xr9:uid="{DB1BEDA7-1027-4FEB-B76F-867979C75A0A}">
+    <tableStyle name="浅色系标题行表格样式_b4126a" count="10" xr9:uid="{867158CB-D5FA-48A5-9440-B5DBE63B955D}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="totalRow" dxfId="14"/>
@@ -2233,6 +2402,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ReportFields_3" displayName="ReportFields_3" ref="A2:F25" totalsRowShown="0">
+  <tableColumns count="6">
+    <tableColumn id="1" name="序号"/>
+    <tableColumn id="2" name="字段名称"/>
+    <tableColumn id="3" name="字段含义"/>
+    <tableColumn id="4" name="示例"/>
+    <tableColumn id="5" name="什么时候提供"/>
+    <tableColumn id="6" name="备注"/>
+  </tableColumns>
+  <tableStyleInfo name="浅色系标题行表格样式_b4126a" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ReportFields" displayName="ReportFields" ref="A2:E52" totalsRowShown="0">
   <tableColumns count="5">
     <tableColumn id="1" name="序号"/>
@@ -2440,902 +2623,618 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8" style="10" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="62" customWidth="1"/>
-    <col min="4" max="4" width="48" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="2" max="2" width="11.4" customWidth="1"/>
+    <col min="3" max="3" width="43.2" customWidth="1"/>
+    <col min="4" max="4" width="26.5" customWidth="1"/>
+    <col min="5" max="5" width="20.9" customWidth="1"/>
+    <col min="10" max="10" width="14.5" customWidth="1"/>
+    <col min="11" max="11" width="26.2" customWidth="1"/>
+    <col min="12" max="12" width="16.7" customWidth="1"/>
+    <col min="13" max="13" width="24.8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="55" customHeight="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="23.4" spans="1:13">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5">
-      <c r="A2" s="11" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="I1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+    </row>
+    <row r="2" ht="33" customHeight="1" spans="1:13">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="B2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="D2" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" ht="21" customHeight="1" spans="1:5">
-      <c r="A3" s="13" t="s">
+      <c r="E2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="F2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="I2" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1" spans="1:13">
+      <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="B3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="C3" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" ht="21" customHeight="1" spans="1:5">
-      <c r="A4" s="13" t="s">
+      <c r="D3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="E3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="I3" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="K3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" ht="21" customHeight="1" spans="1:5">
-      <c r="A5" s="13" t="s">
+      <c r="L3" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="M3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="14" t="s">
+    </row>
+    <row r="4" ht="31" customHeight="1" spans="1:13">
+      <c r="A4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="B4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" ht="21" customHeight="1" spans="1:5">
-      <c r="A6" s="16" t="s">
+      <c r="C4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="D4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="E4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="K4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A7" s="13" t="s">
+      <c r="L4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="M4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="14" t="s">
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:13">
+      <c r="A5" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="B5" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A8" s="13" t="s">
+      <c r="C5" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="D5" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="E5" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="I5" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A9" s="13" t="s">
+      <c r="J5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="K5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="L5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="M5" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1" spans="1:13">
+      <c r="A6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="B6" s="7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A10" s="13" t="s">
+      <c r="C6" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="D6" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="E6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="K6" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A11" s="13" t="s">
+      <c r="L6" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="M6" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1" spans="1:13">
+      <c r="A7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="B7" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="C7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A12" s="13" t="s">
+      <c r="D7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="E7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="K7" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="L7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A13" s="13" t="s">
+      <c r="M7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="14" t="s">
+    </row>
+    <row r="8" ht="31.2" spans="1:13">
+      <c r="A8" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="B8" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="C8" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="D8" s="7" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="14" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A14" s="13" t="s">
+      <c r="E8" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="I8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="K8" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="L8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="M8" s="7" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A15" s="13" t="s">
+    <row r="9" ht="78" spans="1:13">
+      <c r="A9" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B9" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C9" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D9" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="16" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A16" s="13" t="s">
+      <c r="K9" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="L9" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="M9" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="14" t="s">
+    </row>
+    <row r="10" ht="15.6" spans="1:13">
+      <c r="A10" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="B10" s="7" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="17" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A17" s="13" t="s">
+      <c r="C10" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="D10" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="E10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="K10" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="L10" s="7" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="18" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A18" s="13" t="s">
+      <c r="M10" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="14" t="s">
+    </row>
+    <row r="11" ht="15.6" spans="1:13">
+      <c r="A11" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="B11" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="C11" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="D11" s="7" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="19" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A19" s="13" t="s">
+      <c r="E11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+    </row>
+    <row r="12" ht="15.6" spans="1:13">
+      <c r="A12" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B12" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C12" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D12" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E12" s="22" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="20" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A20" s="13" t="s">
+      <c r="F12" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+    </row>
+    <row r="13" ht="31.2" spans="1:13">
+      <c r="A13" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B13" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C13" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D13" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="E20" s="14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A21" s="13" t="s">
+      <c r="E13" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="F13" s="27"/>
+    </row>
+    <row r="14" ht="31.2" spans="1:13">
+      <c r="A14" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="B14" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="C14" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E21" s="14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A22" s="13" t="s">
+      <c r="D14" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="E14" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="14" t="s">
+    </row>
+    <row r="15" ht="46.8" spans="1:13">
+      <c r="A15" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="B15" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="C15" s="7" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="23" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A23" s="13" t="s">
+      <c r="D15" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="E15" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C23" s="14" t="s">
+    </row>
+    <row r="16" ht="15.6" spans="1:13">
+      <c r="A16" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="B16" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="C16" s="7" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A24" s="13" t="s">
+      <c r="D16" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="E16" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="14" t="s">
+    </row>
+    <row r="17" ht="40" customHeight="1" spans="1:6">
+      <c r="A17" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="B17" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="C17" s="7" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="25" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A25" s="13" t="s">
+      <c r="D17" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="E17" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="14" t="s">
+    </row>
+    <row r="18" ht="15.6" spans="1:6">
+      <c r="A18" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="B18" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="C18" s="7" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="26" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A26" s="13" t="s">
+      <c r="D18" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="E18" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C26" s="14" t="s">
+    </row>
+    <row r="19" ht="15.6" spans="1:6">
+      <c r="A19" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="B19" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="E26" s="14" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A27" s="13" t="s">
+      <c r="C19" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="D19" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="E19" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" ht="15.6" spans="1:6">
+      <c r="A20" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="D27" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="E27" s="14" t="s">
+      <c r="B20" s="26" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="28" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A28" s="13" t="s">
+      <c r="C20" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="D20" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="E20" s="26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" ht="15.6" spans="1:6">
+      <c r="A21" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="B21" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="C21" s="29" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="29" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A29" s="13" t="s">
+      <c r="D21" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="E21" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="C29" s="14" t="s">
+    </row>
+    <row r="22" ht="15.6" spans="1:6">
+      <c r="A22" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="B22" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="E29" s="14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="30" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A30" s="13" t="s">
+      <c r="C22" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="D22" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="E22" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="D30" s="14" t="s">
+    </row>
+    <row r="23" ht="31.2" spans="1:6">
+      <c r="A23" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="E30" s="14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A31" s="13" t="s">
+      <c r="B23" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="C23" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="D23" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="D31" s="14" t="s">
+    </row>
+    <row r="24" ht="15.6" spans="1:6">
+      <c r="A24" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="B24" s="22" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="32" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A32" s="13" t="s">
+      <c r="C24" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="D24" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="F24" s="30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" ht="15.6" spans="1:6">
+      <c r="A25" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="B25" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="C25" s="22" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="33" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A33" s="13" t="s">
+      <c r="D25" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="B33" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="E33" s="14" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="34" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A34" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="35" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A35" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="36" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A36" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="37" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A37" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="38" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A38" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="39" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A39" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="40" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A40" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="41" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A41" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="42" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A42" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="43" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A43" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="E43" s="14" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="44" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A44" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="45" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A45" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="E45" s="14" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="46" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A46" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="47" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A47" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="E47" s="14" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="48" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A48" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="49" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A49" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="E49" s="14" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="50" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A50" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="51" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A51" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="C51" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="E51" s="14" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="52" s="9" customFormat="1" ht="21" customHeight="1" spans="1:5">
-      <c r="A52" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="B52" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="55" ht="15" spans="1:5">
-      <c r="A55" s="17" t="s">
-        <v>227</v>
+      <c r="E25" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="I1:M1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -3349,137 +3248,137 @@
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.8" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="8.8" style="1"/>
+    <col min="1" max="1" width="8.8" style="2"/>
     <col min="2" max="2" width="18.4" customWidth="1"/>
     <col min="3" max="3" width="83.7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="33" customHeight="1" spans="1:3">
-      <c r="A1" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="A1" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
     </row>
     <row r="2" ht="17" customHeight="1" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1" spans="1:3">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B3" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1" spans="1:3">
+      <c r="A4" s="11">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1" spans="1:3">
+      <c r="A5" s="11">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" ht="17" customHeight="1" spans="1:3">
-      <c r="A3" s="5">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="4" ht="17" customHeight="1" spans="1:3">
-      <c r="A4" s="5">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="5" ht="17" customHeight="1" spans="1:3">
-      <c r="A5" s="5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>234</v>
+      <c r="B5" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1" spans="1:3">
-      <c r="A6" s="5">
+      <c r="A6" s="11">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>236</v>
+      <c r="B6" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1" spans="1:3">
-      <c r="A7" s="5">
+      <c r="A7" s="11">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>238</v>
+      <c r="B7" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1" spans="1:3">
-      <c r="A8" s="5">
+      <c r="A8" s="11">
         <v>6</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>240</v>
+      <c r="B8" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1" spans="1:3">
-      <c r="A9" s="5">
+      <c r="A9" s="11">
         <v>7</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>242</v>
+      <c r="B9" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1" spans="1:3">
-      <c r="A10" s="5">
+      <c r="A10" s="11">
         <v>8</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>244</v>
+      <c r="B10" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1" spans="1:3">
-      <c r="A11" s="5">
+      <c r="A11" s="11">
         <v>9</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>246</v>
+      <c r="B11" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="12" ht="14.4" spans="1:3">
-      <c r="A12" s="5">
+      <c r="A12" s="11">
         <v>10</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>248</v>
+      <c r="B12" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -3489,4 +3388,910 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="8" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="62" customWidth="1"/>
+    <col min="4" max="4" width="48" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="55" customHeight="1" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1" spans="1:5">
+      <c r="A3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1" spans="1:5">
+      <c r="A4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1" spans="1:5">
+      <c r="A5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1" spans="1:5">
+      <c r="A6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A11" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A12" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A13" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A14" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A15" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A16" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="21" customHeight="1" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="55" ht="15" spans="1:5">
+      <c r="A55" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>